--- a/data/french_works_EdB.xlsx
+++ b/data/french_works_EdB.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>matiere</t>
+          <t>matiere_auto</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Britain</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Britain</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">

--- a/data/french_works_EdB.xlsx
+++ b/data/french_works_EdB.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1283,14 +1272,10 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
           <t>Other</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1303,14 +1288,10 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
           <t>Other</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1323,14 +1304,10 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
           <t>Other</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1343,14 +1320,10 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
           <t>Other</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1363,14 +1336,10 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
           <t>Other</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3187,14 +3156,10 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
           <t>Other</t>
         </is>
       </c>
+      <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">

--- a/data/french_works_EdB.xlsx
+++ b/data/french_works_EdB.xlsx
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Renaut de Montauban, 1re version, 'Vulgate'</t>
+          <t>Renaut de Montauban, 1re version, 'Vulgate</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">

--- a/data/french_works_EdB.xlsx
+++ b/data/french_works_EdB.xlsx
@@ -591,7 +591,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -607,7 +611,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -903,7 +911,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -967,7 +979,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Britain</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3031,7 +3047,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -3207,7 +3227,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -3687,7 +3711,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Britain</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
